--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
@@ -2,59 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28130" windowHeight="12540"/>
   </bookViews>
   <sheets>
-    <sheet name="产品要素调整信息" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>数据状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品登记编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>子产品代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>报告发布日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>巨额赎回日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发的情形说明文字</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拒绝赎回说明（文字）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>产品子代码*</t>
+  </si>
+  <si>
+    <t>产品登记编码*</t>
+  </si>
+  <si>
+    <t>巨额赎回日期（YYYY-MM-DD)*</t>
+  </si>
+  <si>
+    <t>触发的情形说明文字*</t>
+  </si>
+  <si>
+    <t>拒绝赎回说明（文字）*</t>
+  </si>
+  <si>
+    <t>报告发布日期（YYYY-MM-DD)*</t>
   </si>
 </sst>
 </file>
@@ -70,66 +49,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="12"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -140,28 +82,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -174,7 +113,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -216,7 +155,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -251,7 +190,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -460,46 +399,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="22.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" customWidth="1"/>
+    <col min="4" max="4" width="22.90625" customWidth="1"/>
+    <col min="5" max="5" width="29.6328125" customWidth="1"/>
+    <col min="6" max="6" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28130" windowHeight="12540"/>
   </bookViews>
@@ -82,7 +87,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -94,6 +99,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -404,7 +415,7 @@
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" style="5" customWidth="1"/>
     <col min="4" max="4" width="22.90625" customWidth="1"/>
     <col min="5" max="5" width="29.6328125" customWidth="1"/>
     <col min="6" max="6" width="27.26953125" customWidth="1"/>
@@ -417,7 +428,7 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>产品子代码*</t>
   </si>
@@ -39,6 +39,18 @@
   </si>
   <si>
     <t>报告发布日期（YYYY-MM-DD)*</t>
+  </si>
+  <si>
+    <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -410,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -419,26 +431,36 @@
     <col min="4" max="4" width="22.90625" customWidth="1"/>
     <col min="5" max="5" width="29.6328125" customWidth="1"/>
     <col min="6" max="6" width="27.26953125" customWidth="1"/>
+    <col min="7" max="7" width="24.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28130" windowHeight="12540"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>产品子代码*</t>
   </si>
@@ -50,6 +50,10 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子产品名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -422,19 +426,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22.90625" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" customWidth="1"/>
-    <col min="7" max="7" width="24.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="4" width="29.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.875" customWidth="1"/>
+    <col min="6" max="6" width="29.625" customWidth="1"/>
+    <col min="7" max="7" width="27.25" customWidth="1"/>
+    <col min="8" max="8" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -444,22 +448,25 @@
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -473,7 +480,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -484,7 +491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
@@ -41,10 +41,6 @@
     <t>报告发布日期（YYYY-MM-DD)*</t>
   </si>
   <si>
-    <t>数据状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>更新时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -54,6 +50,10 @@
   </si>
   <si>
     <t>子产品名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -429,45 +429,45 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11.875" customWidth="1"/>
-    <col min="3" max="4" width="29.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.875" customWidth="1"/>
-    <col min="6" max="6" width="29.625" customWidth="1"/>
-    <col min="7" max="7" width="27.25" customWidth="1"/>
-    <col min="8" max="8" width="24.75" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="3" width="29.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="29.625" customWidth="1"/>
+    <col min="6" max="6" width="27.25" customWidth="1"/>
+    <col min="7" max="7" width="24.75" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro.xlsx
@@ -32,9 +32,6 @@
     <t>巨额赎回日期（YYYY-MM-DD)*</t>
   </si>
   <si>
-    <t>触发的情形说明文字*</t>
-  </si>
-  <si>
     <t>拒绝赎回说明（文字）*</t>
   </si>
   <si>
@@ -54,6 +51,10 @@
   </si>
   <si>
     <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的情形说明文字（文字）*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -446,28 +447,28 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
